--- a/artfynd/A 4580-2025 artfynd.xlsx
+++ b/artfynd/A 4580-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,6 +945,286 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/96850702</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137428645</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>694461</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6659961</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2 m upp</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 2 m upp</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428645</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137428652</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>694362</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6659977</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>3 m upp</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 3 m upp</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428652</t>
         </is>
       </c>
     </row>
@@ -952,6 +1232,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
